--- a/hrm/.plans/elearning-quan-ly/danh-muc-ky-nang/testcase.xlsx
+++ b/hrm/.plans/elearning-quan-ly/danh-muc-ky-nang/testcase.xlsx
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -702,7 +702,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Danh sách phẳng, không phân cấp. Mỗi kỹ năng có lịch sử thay đổi riêng (xem qua nút Lịch sử).</t>
+          <t>Danh sách phẳng, không phân cấp. Mỗi kỹ năng có tên + Icon (class Remix, không bắt buộc) + trạng thái + lịch sử thay đổi riêng (xem qua nút Lịch sử).</t>
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -794,7 +794,7 @@
       <c r="N9" s="4" t="n"/>
       <c r="O9" s="5" t="n"/>
     </row>
-    <row r="10" ht="40" customHeight="1">
+    <row r="10" ht="46" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>9. Ghi chú đọc bảng</t>
@@ -802,7 +802,8 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Mặc định 10 dòng/trang, sắp xếp theo Cập nhật mới nhất. Cột Cập nhật hiện ngày + tên người cập nhật. Xuất Excel/In theo đúng bộ lọc đang áp.</t>
+          <t>Mặc định 10 dòng/trang, sắp xếp theo Cập nhật mới nhất. Cột Cập nhật hiện ngày + tên người cập nhật. Bảng có cột Icon (chip) rộng ~80px canh giữa. Xuất Excel/In theo đúng bộ lọc đang áp.
+LƯU Ý GIỚI HẠN: icon đã chọn hiện chưa trả về ở API danh sách + filter-options elearning nên chip Icon ở bảng và dropdown 'Học theo kỹ năng' hiện tạm luôn hiển thị icon mặc định ri-lightbulb-line; modal Sửa vẫn đúng icon đã lưu.</t>
         </is>
       </c>
       <c r="C10" s="4" t="n"/>
@@ -2486,7 +2487,7 @@
       <c r="B42" s="11" t="n"/>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>IV. XUẤT EXCEL / IN</t>
+          <t>IV. ICON KỸ NĂNG</t>
         </is>
       </c>
       <c r="D42" s="4" t="n"/>
@@ -2502,7 +2503,7 @@
       <c r="N42" s="4" t="n"/>
       <c r="O42" s="5" t="n"/>
     </row>
-    <row r="43" ht="30" customHeight="1">
+    <row r="43" ht="40" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Kỹ năng</t>
@@ -2510,7 +2511,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>XUẤT EXCEL / IN</t>
+          <t>ICON KỸ NĂNG</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -2520,7 +2521,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Xuất Excel theo bộ lọc</t>
+          <t>Chọn icon khi thêm mới</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -2530,27 +2531,31 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Đang lọc từ khóa 'Lập trình'</t>
+          <t>Popup 'Thêm mới kỹ năng' đang mở</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1. Bấm 'Xuất Excel'</t>
+          <t>1. Bấm swatch 'Icon'
+2. Panel lưới icon (7 cột) mở, chọn 1 icon (vd Bóng đèn)
+3. Nhập Tên = 'Kỹ năng có icon'
+4. Bấm 'Lưu'</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>Từ khóa: Lập trình</t>
+          <t>Icon: ri-lightbulb-line</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>- Tải file danh_sach_ky_nang.xls chứa đúng kỹ năng đang lọc</t>
+          <t>- Toast 'Lưu thành công'
+- Kỹ năng được lưu kèm icon đã chọn</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>Xuất theo bộ lọc hiện tại</t>
+          <t>Icon không bắt buộc, lưu class Remix</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr"/>
@@ -2579,7 +2584,7 @@
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>XUẤT EXCEL / IN</t>
+          <t>ICON KỸ NĂNG</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
@@ -2589,37 +2594,40 @@
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>In danh sách</t>
+          <t>Thêm mới KHÔNG chọn icon</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>Đang lọc Trạng thái = Hoạt động</t>
+          <t>Popup 'Thêm mới kỹ năng' đang mở</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>1. Bấm 'In'</t>
+          <t>1. Chỉ nhập Tên = 'Kỹ năng không icon'
+2. Không chọn icon
+3. Bấm 'Lưu'</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Trạng thái: Hoạt động</t>
+          <t>Icon: (không chọn)</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>- Mở tab mới hiển thị bản in danh sách đúng bộ lọc</t>
+          <t>- Lưu thành công bình thường (icon không bắt buộc)
+- icon = null</t>
         </is>
       </c>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BR-09 (icon nullable)</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr"/>
@@ -2640,114 +2648,625 @@
       </c>
       <c r="O44" s="14" t="inlineStr"/>
     </row>
-    <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="11" t="n"/>
-      <c r="B45" s="11" t="n"/>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>V. LUỒNG XUYÊN SUỐT (E2E)</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n"/>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="n"/>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" s="4" t="n"/>
-      <c r="L45" s="4" t="n"/>
-      <c r="M45" s="4" t="n"/>
-      <c r="N45" s="4" t="n"/>
-      <c r="O45" s="5" t="n"/>
-    </row>
-    <row r="46" ht="57" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>Kỹ năng</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>ICON KỸ NĂNG</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>TC_04.003</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Bỏ chọn icon</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Panel icon đang mở, đã chọn 1 icon</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>1. Bấm 'Bỏ chọn'</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>- Icon được xóa lựa chọn (về trống)</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr"/>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>Kỹ năng</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>ICON KỸ NĂNG</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>TC_04.004</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>Sửa đổi icon của kỹ năng</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>Kỹ năng 'Kế toán' đang Hoạt động, đã có icon A</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>1. Bấm Sửa 'Kế toán'
+2. Modal hiện đúng icon A đang lưu
+3. Chọn icon B khác
+4. Bấm 'Lưu'</t>
+        </is>
+      </c>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>Icon mới: B</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>- Toast 'Lưu thành công'
+- Icon cập nhật thành B
+- Lịch sử ghi thay đổi trường icon (A→B)</t>
+        </is>
+      </c>
+      <c r="J46" s="14" t="inlineStr">
+        <is>
+          <t>BR-10 (ghi log icon)</t>
+        </is>
+      </c>
+      <c r="K46" s="14" t="inlineStr"/>
+      <c r="L46" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M46" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N46" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="O46" s="14" t="inlineStr"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Kỹ năng</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>ICON KỸ NĂNG</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>TC_04.005</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Modal Sửa hiển thị đúng icon đã lưu</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Kỹ năng đã lưu icon 'ri-brain-line'</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>1. Bấm Sửa kỹ năng đó</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>- Swatch Icon trong modal hiển thị đúng 'ri-brain-line' đã lưu</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>API chi tiết trả model gốc có icon</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr"/>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>Kỹ năng</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>ICON KỸ NĂNG</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>TC_04.006</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>Chip Icon ở bảng danh sách (giới hạn hiện tại)</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>Kỹ năng đã chọn icon khác mặc định</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>1. Xem cột Icon ở bảng danh sách</t>
+        </is>
+      </c>
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>- Hiện chip icon; hiện tại luôn là icon mặc định ri-lightbulb-line do API danh sách chưa trả cột icon (giới hạn đã biết)</t>
+        </is>
+      </c>
+      <c r="J48" s="14" t="inlineStr">
+        <is>
+          <t>GAP: SkillListResource chưa trả icon</t>
+        </is>
+      </c>
+      <c r="K48" s="14" t="inlineStr"/>
+      <c r="L48" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M48" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N48" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="O48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49" ht="39" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Kỹ năng</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>ICON KỸ NĂNG</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>TC_04.007</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Icon ở dropdown 'Học theo kỹ năng' elearning (giới hạn)</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Kỹ năng công khai có icon riêng</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>1. Mở portal elearning
+2. Mở dropdown 'Học theo kỹ năng' trên header</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>- Mỗi kỹ năng có icon; hiện tại luôn hiển thị icon mặc định do filter-options chưa select cột icon (giới hạn đã biết)</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>GAP: PublicBrowseController.filterOptions chưa select icon</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr"/>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="11" t="n"/>
+      <c r="B50" s="11" t="n"/>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>V. XUẤT EXCEL / IN</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n"/>
+      <c r="J50" s="4" t="n"/>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="n"/>
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="5" t="n"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>Kỹ năng</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>XUẤT EXCEL / IN</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>TC_05.001</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>Xuất Excel theo bộ lọc</t>
+        </is>
+      </c>
+      <c r="E51" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>Đang lọc từ khóa 'Lập trình'</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>1. Bấm 'Xuất Excel'</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>Từ khóa: Lập trình</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
+          <t>- Tải file danh_sach_ky_nang.xls chứa đúng kỹ năng đang lọc</t>
+        </is>
+      </c>
+      <c r="J51" s="14" t="inlineStr">
+        <is>
+          <t>Xuất theo bộ lọc hiện tại</t>
+        </is>
+      </c>
+      <c r="K51" s="14" t="inlineStr"/>
+      <c r="L51" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M51" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N51" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="O51" s="14" t="inlineStr"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Kỹ năng</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>XUẤT EXCEL / IN</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>TC_05.002</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>In danh sách</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Đang lọc Trạng thái = Hoạt động</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>1. Bấm 'In'</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Trạng thái: Hoạt động</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>- Mở tab mới hiển thị bản in danh sách đúng bộ lọc</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr"/>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="11" t="n"/>
+      <c r="B53" s="11" t="n"/>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>VI. LUỒNG XUYÊN SUỐT (E2E)</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="n"/>
+      <c r="G53" s="4" t="n"/>
+      <c r="H53" s="4" t="n"/>
+      <c r="I53" s="4" t="n"/>
+      <c r="J53" s="4" t="n"/>
+      <c r="K53" s="4" t="n"/>
+      <c r="L53" s="4" t="n"/>
+      <c r="M53" s="4" t="n"/>
+      <c r="N53" s="4" t="n"/>
+      <c r="O53" s="5" t="n"/>
+    </row>
+    <row r="54" ht="65" customHeight="1">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>Kỹ năng</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>LUỒNG XUYÊN SUỐT (E2E)</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>TC_05.001</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>TC_06.001</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
         <is>
           <t>Vòng đời 1 kỹ năng</t>
         </is>
       </c>
-      <c r="E46" s="13" t="inlineStr">
+      <c r="E54" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F54" s="14" t="inlineStr">
         <is>
           <t>Có quyền Quản lý kỹ năng</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>1. Thêm mới 'Kỹ năng test'
-2. Sửa tên thành 'Kỹ năng test 2'
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>1. Thêm mới 'Kỹ năng test' + chọn icon
+2. Sửa tên thành 'Kỹ năng test 2' + đổi icon
 3. Xem Lịch sử
 4. Khóa
 5. Mở khóa
 6. Xóa</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="H54" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>- B1: tạo thành công, trạng thái Hoạt động
-- B2: đổi tên OK
-- B3: lịch sử hiện tên cũ→mới
+      <c r="I54" s="14" t="inlineStr">
+        <is>
+          <t>- B1: tạo thành công kèm icon, trạng thái Hoạt động
+- B2: đổi tên + icon OK
+- B3: lịch sử hiện thay đổi tên &amp; icon
 - B4: trạng thái Khóa, ẩn nút
 - B5: trạng thái Hoạt động
 - B6: xóa khỏi danh sách</t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr">
+      <c r="J54" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr"/>
+      <c r="K54" s="14" t="inlineStr"/>
+      <c r="L54" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M54" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N54" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="O54" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="29">
     <mergeCell ref="B4:O4"/>
     <mergeCell ref="B7:O7"/>
     <mergeCell ref="B3:O3"/>
     <mergeCell ref="I12:K12"/>
     <mergeCell ref="L11:O11"/>
     <mergeCell ref="C28:O28"/>
+    <mergeCell ref="C53:O53"/>
     <mergeCell ref="I14:K14"/>
     <mergeCell ref="B2:O2"/>
     <mergeCell ref="C18:O18"/>
@@ -2756,7 +3275,6 @@
     <mergeCell ref="B8:O8"/>
     <mergeCell ref="L13:O13"/>
     <mergeCell ref="I13:K13"/>
-    <mergeCell ref="C45:O45"/>
     <mergeCell ref="C35:O35"/>
     <mergeCell ref="B10:O10"/>
     <mergeCell ref="L12:O12"/>
@@ -2766,13 +3284,14 @@
     <mergeCell ref="I15:K15"/>
     <mergeCell ref="B9:O9"/>
     <mergeCell ref="I11:K11"/>
+    <mergeCell ref="C50:O50"/>
     <mergeCell ref="L14:O14"/>
     <mergeCell ref="B6:O6"/>
     <mergeCell ref="B5:O5"/>
     <mergeCell ref="C21:O21"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="L18:N147" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L18:N155" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Passed,Failed,Pending,Not Executed"</formula1>
     </dataValidation>
   </dataValidations>
